--- a/成品提交/支撑材料/结果文件/result1.xlsx
+++ b/成品提交/支撑材料/结果文件/result1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\28623\Desktop\学习\GT学业\CUMCM2026\成品提交\支撑材料\结果文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813C9406-D12E-4972-8E13-ED1C0BB977C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED255DB3-55E8-4314-838B-2AFD2F8156A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,223 +333,223 @@
   </si>
   <si>
     <t>时间段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0:50-1:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1:00-1:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1:50-2:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2:00-2:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2:50-3:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>3:00-3:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>3:50-4:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4:00-4:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4:50-5:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>5:00-5:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>5:50-6:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>6:00-6:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>6:50-7:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>7:00-7:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>7:50-8:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>8:00-8:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>8:50-9:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>9:00-9:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>9:50-10:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10:00-10:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10:50-11:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>11:00-11:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>11:50-12:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>12:00-12:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>12:50-13:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>13:00-13:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>13:50-14:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>14:00-14:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>14:50-15:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>15:00-15:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>15:50-16:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>16:00-16:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>16:50-17:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>17:00-17:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>17:50-18:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>18:00-18:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>18:50-19:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>19:00-19:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>19:50-20:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>20:00-20:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>20:50-21:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>21:00-21:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>21:50-22:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>22:00-22:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>22:50-23:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>23:00-23:10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>23:50-0:00+1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0:00+1-0:10+1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>购电量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0:00-4:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>充电量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>放电量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>24:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -568,12 +568,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -583,6 +577,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -610,17 +610,17 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -928,11 +928,11 @@
   <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -940,7 +940,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2">
@@ -948,7 +948,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
@@ -956,31 +956,31 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1407.3839</v>
+        <v>574.05050000000006</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1409.0739000000001</v>
+        <v>575.74059999999997</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B6">
-        <v>1409.8045999999999</v>
+        <v>576.47119999999995</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B7">
@@ -988,7 +988,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B8">
@@ -996,7 +996,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B9">
@@ -1004,15 +1004,15 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B10">
-        <v>911.16139999999996</v>
+        <v>577.82799999999997</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11">
@@ -1020,7 +1020,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B12">
@@ -1028,7 +1028,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B13">
@@ -1036,7 +1036,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14">
@@ -1044,7 +1044,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B15">
@@ -1052,7 +1052,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B16">
@@ -1060,7 +1060,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B17">
@@ -1068,7 +1068,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B18">
@@ -1076,7 +1076,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B19">
@@ -1084,7 +1084,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B20">
@@ -1092,7 +1092,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B21">
@@ -1100,7 +1100,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B22">
@@ -1108,7 +1108,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B23">
@@ -1116,7 +1116,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B24">
@@ -1124,7 +1124,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B25">
@@ -1132,7 +1132,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B26">
@@ -1140,7 +1140,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B27">
@@ -1148,7 +1148,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B28">
@@ -1156,7 +1156,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B29">
@@ -1164,7 +1164,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B30">
@@ -1172,7 +1172,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B31">
@@ -1180,7 +1180,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B32">
@@ -1188,7 +1188,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B33">
@@ -1196,7 +1196,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B34">
@@ -1204,7 +1204,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B35">
@@ -1212,7 +1212,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B36">
@@ -1220,7 +1220,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B37">
@@ -1228,7 +1228,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B38">
@@ -1236,7 +1236,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B39">
@@ -1244,7 +1244,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B40">
@@ -1252,7 +1252,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B41">
@@ -1260,7 +1260,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>116</v>
       </c>
       <c r="B42">
@@ -1268,7 +1268,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B43">
@@ -1276,7 +1276,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B44">
@@ -1284,7 +1284,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B45">
@@ -1292,7 +1292,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B46">
@@ -1300,7 +1300,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B47">
@@ -1308,7 +1308,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B48">
@@ -1316,7 +1316,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B49">
@@ -1324,7 +1324,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B50">
@@ -1332,7 +1332,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B51">
@@ -1340,7 +1340,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B52">
@@ -1348,7 +1348,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B53">
@@ -1356,7 +1356,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B54">
@@ -1364,7 +1364,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B55">
@@ -1372,7 +1372,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B56">
@@ -1380,7 +1380,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B57">
@@ -1388,7 +1388,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B58">
@@ -1396,7 +1396,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B59">
@@ -1404,7 +1404,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B60">
@@ -1412,7 +1412,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B61">
@@ -1420,7 +1420,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B62">
@@ -1428,7 +1428,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B63">
@@ -1436,7 +1436,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B64">
@@ -1444,7 +1444,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B65">
@@ -1452,7 +1452,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B66">
@@ -1460,7 +1460,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B67">
@@ -1468,7 +1468,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B68">
@@ -1476,7 +1476,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B69">
@@ -1484,7 +1484,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B70">
@@ -1492,7 +1492,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B71">
@@ -1500,7 +1500,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B72">
@@ -1508,7 +1508,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B73">
@@ -1516,7 +1516,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B74">
@@ -1524,7 +1524,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B75">
@@ -1532,7 +1532,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B76">
@@ -1540,7 +1540,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B77">
@@ -1548,7 +1548,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B78">
@@ -1556,7 +1556,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B79">
@@ -1564,7 +1564,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B80">
@@ -1572,7 +1572,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B81">
@@ -1580,7 +1580,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B82">
@@ -1588,7 +1588,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B83">
@@ -1596,7 +1596,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B84">
@@ -1604,7 +1604,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B85">
@@ -1612,7 +1612,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B86">
@@ -1620,7 +1620,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B87">
@@ -1628,7 +1628,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B88">
@@ -1636,7 +1636,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B89">
@@ -1644,7 +1644,7 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B90">
@@ -1652,7 +1652,7 @@
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B91">
@@ -1660,7 +1660,7 @@
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B92">
@@ -1668,7 +1668,7 @@
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B93">
@@ -1676,7 +1676,7 @@
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B94">
@@ -1684,7 +1684,7 @@
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B95">
@@ -1692,7 +1692,7 @@
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B96">
@@ -1700,7 +1700,7 @@
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B97">
@@ -1708,7 +1708,7 @@
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B98">
@@ -1716,7 +1716,7 @@
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B99">
@@ -1724,7 +1724,7 @@
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B100">
@@ -1732,7 +1732,7 @@
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B101">
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B102">
@@ -1748,7 +1748,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B103">
@@ -1756,7 +1756,7 @@
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B104">
@@ -1764,7 +1764,7 @@
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B105">
@@ -1772,7 +1772,7 @@
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B106">
@@ -1780,7 +1780,7 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B107">
@@ -1788,7 +1788,7 @@
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B108">
@@ -1796,7 +1796,7 @@
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B109">
@@ -1804,7 +1804,7 @@
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B110">
@@ -1812,7 +1812,7 @@
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B111">
@@ -1820,7 +1820,7 @@
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B112">
@@ -1828,7 +1828,7 @@
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B113">
@@ -1836,7 +1836,7 @@
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B114">
@@ -1844,7 +1844,7 @@
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B115">
@@ -1852,7 +1852,7 @@
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B116">
@@ -1860,7 +1860,7 @@
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B117">
@@ -1868,7 +1868,7 @@
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B118">
@@ -1876,7 +1876,7 @@
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B119">
@@ -1884,7 +1884,7 @@
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B120">
@@ -1892,7 +1892,7 @@
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B121">
@@ -1900,7 +1900,7 @@
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B122">
@@ -1908,7 +1908,7 @@
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B123">
@@ -1916,7 +1916,7 @@
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B124">
@@ -1924,7 +1924,7 @@
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B125">
@@ -1932,7 +1932,7 @@
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B126">
@@ -1940,7 +1940,7 @@
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B127">
@@ -1948,7 +1948,7 @@
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B128">
@@ -1956,7 +1956,7 @@
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B129">
@@ -1964,7 +1964,7 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B130">
@@ -1972,7 +1972,7 @@
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B131">
@@ -1980,7 +1980,7 @@
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B132">
@@ -1988,7 +1988,7 @@
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B133">
@@ -1996,7 +1996,7 @@
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B134">
@@ -2004,7 +2004,7 @@
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B135">
@@ -2012,7 +2012,7 @@
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B136">
@@ -2020,7 +2020,7 @@
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B137">
@@ -2028,15 +2028,15 @@
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B138">
-        <v>566.74739999999997</v>
+        <v>1400.0808</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B139">
@@ -2044,23 +2044,23 @@
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B140">
-        <v>567.83019999999999</v>
+        <v>1234.4967999999999</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B141">
-        <v>902.69200000000001</v>
+        <v>1402.692</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B142">
@@ -2068,15 +2068,15 @@
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B143">
-        <v>571.61540000000002</v>
+        <v>1404.9486999999999</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B144">
@@ -2084,7 +2084,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B145">
@@ -2092,7 +2092,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2106,29 +2106,29 @@
     <col min="4" max="4" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B2">
-        <v>4500</v>
+        <v>1666.6667</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2137,11 +2137,11 @@
         <v>156</v>
       </c>
       <c r="E2">
-        <v>6000</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B3">
@@ -2154,11 +2154,11 @@
         <v>157</v>
       </c>
       <c r="E3">
-        <v>6000</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B4">
@@ -2167,10 +2167,10 @@
       <c r="C4">
         <v>2121.4184</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B5">
@@ -2179,10 +2179,10 @@
       <c r="C5">
         <v>91.101399999999998</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B6">
@@ -2191,22 +2191,22 @@
       <c r="C6">
         <v>5068.6868999999997</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B7">
-        <v>5333.3333000000002</v>
+        <v>8166.6666999999998</v>
       </c>
       <c r="C7">
         <v>3571.3130999999998</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>